--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.103.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.103.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.103.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.103.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -602,11 +602,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE MASTERâ€™S OFFICE.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]96</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]96</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L16: isolated marker/symbol line :: 96</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]96</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -657,7 +661,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: terâ€™s office is</t>
+          <t>L115: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -667,7 +671,11 @@
           <t>L73: isolated marker/symbol line :: A</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L115: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
@@ -702,11 +710,7 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -739,7 +743,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -754,7 +758,7 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: Â·</t>
+          <t>L80: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -938,7 +942,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -977,7 +981,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1016,7 +1020,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
